--- a/consent_forms/035_travel_safety_measures_acknowledgement_form--consent_forms.xlsx
+++ b/consent_forms/035_travel_safety_measures_acknowledgement_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,64 +520,76 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>travel_safety_measures_1</t>
+          <t>i_acknowledge_that_i_have_completed_a_pre_trip_travel_risk_assessment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>travel_safety_measures</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>I Acknowledge That I Have Completed A Pre Trip Travel Risk Assessment</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please confirm that you have completed a pre-trip travel risk assessment.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>travel_safety_measures_1</t>
+          <t>have_i_familiarized_myself_with_all_emergency_procedure_documents</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>i_acknowledge_that_i_have_completed_a_pre_trip_travel_risk_assessment</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Have I Familiarized Myself With All Emergency Procedure Documents?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please confirm that you have read and understood all emergency procedure documents.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>travel_safety_measures_2</t>
+          <t>will_i_conduct_a_risk_assessment_on_return</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>have_i_fully_understood_the_emergency_response_and_emergency_evacuation_plans</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Will I Conduct A Risk Assessment On Return?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please confirm that you will conduct a risk assessment on return.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,41 +601,49 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>travel_safety_measures_3</t>
+          <t>will_i_adhere_to_all_emergency_response_and_emergency_evacuation_procedures</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>will_i_adhere_to_all_emergency_response_and_evacuation_procedures</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Will I Adhere To All Emergency Response And Emergency Evacuation Procedures?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please confirm that you will adhere to all emergency response and emergency evacuation procedures.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>travel_safety_measures_4</t>
+          <t>will_i_report_any_emergency_situations_to_my_manager</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>have_i_read_and_familiarized_myself_with_all_emergency_procedure_documents</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Will I Report Any Emergency Situations To My Manager?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please confirm that you will report any emergency situations to your manager.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,41 +655,49 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>travel_safety_measures_5</t>
+          <t>will_i_ask_my_manager_to_review_the_emergency_response_and_emergency_evacuation_plans</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>i_understand_that_i_am_responsible_for_my_own_safety_and_well_being_while_traveling</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Will I Ask My Manager To Review The Emergency Response And Emergency Evacuation Plans?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please confirm that you will ask your manager to review the emergency response and emergency evacuation plans.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>travel_safety_measures_6</t>
+          <t>have_i_asked_my_manager_to_review_the_emergency_response_and_emergency_evacuation_plans</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>i_will_conduct_a_pre_trip_risk_assessment</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Have I Asked My Manager To Review The Emergency Response And Emergency Evacuation Plans?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please confirm that you have asked your manager to review the emergency response and emergency evacuation plans.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,64 +709,76 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>travel_safety_measures_7</t>
+          <t>travel_safety_measures_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>will_i_report_any_emergency_situations_to_my_manager</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Emergency Safety Measures Taken</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please describe the emergency safety measures taken.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>travel_safety_measures_8</t>
+          <t>pre_travel_risk_assessment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>travel_safety_measures</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Pre-Travel Risk Assessment</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please enter date of pre-trip risk assessment.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>travel_safety_measures_9</t>
+          <t>emergency_contact</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>travel_safety_measures</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Emergency Contact</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please enter your emergency contact person name and phone number.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,110 +790,130 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>travel_safety_measures_10</t>
+          <t>travel_safety_measures</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>travel_safety_measures</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Travel Safety Measures</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please choose one of the emergency response options.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>travel_safety_measures_11</t>
+          <t>will_i_report_any_emergency_situations_to_my_manager_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>will_i_conduct_a_risk_assessment_on_return</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Will I Report Any Emergency Situations To My Manager 2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please choose one of the emergency response options.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>travel_safety_measures_12</t>
+          <t>have_i_completed_a_pre_trip_travel_risk_assessment</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>will_i_report_any_emergency_situations_to_my_manager</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Have I Completed A Pre Trip Travel Risk Assessment</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please confirm that you have completed a pre-trip travel risk assessment.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>travel_safety_measures_13</t>
+          <t>will_i_read_all_emergency_procedure_documents</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>travel_safety_measures</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Will I Read All Emergency Procedure Documents?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please confirm that you will read all emergency procedure documents.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>travel_safety_measures_14</t>
+          <t>travel_safety_measures_1_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>travel_safety_measures</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Travel Safety Measures 1 2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please choose one of the travel safety options.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,18 +925,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>travel_safety_measures_15</t>
+          <t>will_i_ask_my_manager_to_review_the_emergency_response_and_emergency_evacuation_plans_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>have_i_read_all_the_emergency_procedure_documents</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Will I Ask My Manager To Review The Emergency Response And Emergency Evacuation Plans 2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please confirm that you will ask your manager to review the emergency response and emergency evacuation plans.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,18 +952,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>travel_safety_measures_16</t>
+          <t>have_i_conducted_a_pre_trip_risk_assessment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>have_i_familiarized_myself_with_all_emergency_procedure_documents</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Have I Conducted A Pre Trip Risk Assessment?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please confirm that you have conducted a pre-trip risk assessment.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,41 +979,49 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>travel_safety_measures_17</t>
+          <t>have_i_reviewed_all_emergency_response_and_emergency_evacuation_plans</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>have_i_asked_my_manager_to_review_the_emergency_response_and_emergency_evacuation_plans</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Have I Reviewed All Emergency Response And Emergency Evacuation Plans?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please confirm that you have reviewed all emergency response and emergency evacuation plans.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>have_i_completed_all_emergency_response_and_emergency_evacuation_plans</t>
+          <t>will_i_conduct_a_risk_assessment_on_return_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Have I Completed All Emergency Response And Emergency Evacuation Plans</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Will I Conduct A Risk Assessment On Return 2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Please confirm that you will conduct a risk assessment on return.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -957,18 +1033,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>have_i_completed_a_pre_trip_travel_risk_assessment</t>
+          <t>will_i_review_all_emergency_response_and_emergency_evacuation_plans</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Have I Completed A Pre Trip Travel Risk Assessment</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Will I Review All Emergency Response And Emergency Evacuation Plans?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Please confirm that you will review all emergency response and emergency evacuation plans.</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -980,110 +1060,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>travel_safety_measures_1</t>
+          <t>have_i_fully_understood_the_emergency_response_and_emergency_evacuation_plans</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>emergency_safety_measures_taken</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Have I Fully Understood The Emergency Response And Emergency Evacuation Plans?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Please confirm that you have fully understood the emergency response and emergency evacuation plans.</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>travel_safety_measures_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>pre_travel_risk_assessment</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>travel_safety_measures_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>emergency_contact</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>travel_safety_measures_4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>travel_safety_measures</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>travel_safety_measures_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>travel_safety_measures</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1090,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,340 +1118,408 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>travel_safety_measures_1_choices</t>
+          <t>will_i_conduct_a_risk_assessment_on_return_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>travel_safety_measures_1_choices</t>
+          <t>will_i_conduct_a_risk_assessment_on_return_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>travel_safety_measures_1_choices</t>
+          <t>will_i_conduct_a_risk_assessment_on_return_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>travel_safety_measures_3_choices</t>
+          <t>will_i_adhere_to_all_emergency_response_and_emergency_evacuation_procedures_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>travel_safety_measures_3_choices</t>
+          <t>will_i_adhere_to_all_emergency_response_and_emergency_evacuation_procedures_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>travel_safety_measures_3_choices</t>
+          <t>will_i_adhere_to_all_emergency_response_and_emergency_evacuation_procedures_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>travel_safety_measures_6_choices</t>
+          <t>will_i_report_any_emergency_situations_to_my_manager_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>travel_safety_measures_6_choices</t>
+          <t>will_i_report_any_emergency_situations_to_my_manager_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>travel_safety_measures_8_choices</t>
+          <t>will_i_report_any_emergency_situations_to_my_manager_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>travel_safety_measures_8_choices</t>
+          <t>travel_safety_measures_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>travel_safety_measures_8_choices</t>
+          <t>travel_safety_measures_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>travel_safety_measures_9_choices</t>
+          <t>travel_safety_measures_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>travel_safety_measures_9_choices</t>
+          <t>will_i_report_any_emergency_situations_to_my_manager_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>travel_safety_measures_9_choices</t>
+          <t>will_i_report_any_emergency_situations_to_my_manager_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>travel_safety_measures_10_choices</t>
+          <t>will_i_report_any_emergency_situations_to_my_manager_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>travel_safety_measures_10_choices</t>
+          <t>will_i_read_all_emergency_procedure_documents_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>travel_safety_measures_10_choices</t>
+          <t>will_i_read_all_emergency_procedure_documents_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>travel_safety_measures_12_choices</t>
+          <t>will_i_read_all_emergency_procedure_documents_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>travel_safety_measures_12_choices</t>
+          <t>travel_safety_measures_1_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>travel_safety_measures_12_choices</t>
+          <t>travel_safety_measures_1_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>travel_safety_measures_1_2_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>will_i_conduct_a_risk_assessment_on_return_2_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>will_i_conduct_a_risk_assessment_on_return_2_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>will_i_conduct_a_risk_assessment_on_return_2_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
